--- a/reports/jobs_2026-09-03.xlsx
+++ b/reports/jobs_2026-09-03.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>AI Engineer (Platform)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729957005</t>
+          <t>https://careers.arm.com/job/bengaluru/engineer/33099/100112429248</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -565,57 +565,57 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Setu</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Data Engineer Engineering Â· Data Apply</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>https://pinelabsgroup.turbohire.co/get/aDFnNUx</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>https://setu.co/careers</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Agnikul Cosmos</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>mailto:%20humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>https://agnikul.in/careers</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Agnikul Cosmos</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
+          <t>Chiang Mai 1 available jobs</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -628,7 +628,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -636,12 +640,12 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://agnikul.in/careers</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -658,7 +662,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai 1 available jobs</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -683,7 +687,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -705,7 +709,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Mumbai 0 available jobs</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -730,7 +734,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -752,7 +756,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs</t>
+          <t>Shanghai 0 available jobs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -777,7 +781,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -799,7 +803,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 0 available jobs</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -812,11 +816,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -824,7 +824,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -859,7 +859,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai jobs Yokohama jobs</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -867,7 +871,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -889,12 +893,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -902,11 +906,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -914,7 +914,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1017,12 +1017,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Atlan</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>Field Security Engineer</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1035,7 +1035,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -1043,12 +1047,12 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://jobs.ashbyhq.com/atlan</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1060,12 +1064,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Theorem Proving Engineer</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1086,12 +1090,12 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1103,12 +1107,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Embedded Compiler Engineer (Machine Learning)</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1129,12 +1133,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/lund/embedded-compiler-engineer-machine-learning/33099/94847322016</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1146,12 +1150,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Atlan</t>
+          <t>Cloudflare India</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Field Security Engineer</t>
+          <t>Customer Engineer, India (Based in Mumbai)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1166,7 +1170,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Remote India</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1176,12 +1180,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
+          <t>https://boards.greenhouse.io/cloudflare/jobs/7955378?gh_jid=7955378</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan</t>
+          <t>https://boards.greenhouse.io/cloudflare</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1193,17 +1197,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Databricks India</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1211,7 +1215,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Remote - India</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -1219,12 +1227,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1236,17 +1244,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1254,7 +1262,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Gurgaon Full-time</t>
+        </is>
+      </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -1262,12 +1274,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://exotel.com/about-us/careers/#op-689879-implementation-engineer-</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1279,17 +1291,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Cloudflare India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Customer Engineer, India (Based in Mumbai)</t>
+          <t>Integration &amp; Customisation Engineer (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1299,7 +1311,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Remote India</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1309,12 +1321,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/cloudflare/jobs/7955378?gh_jid=7955378</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-php--reactjs</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/cloudflare</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1326,17 +1338,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Databricks India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Product Support Intern (API Integration)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1346,7 +1358,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1356,12 +1368,12 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
+          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-api-integration</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/databricks</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1378,7 +1390,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1393,7 +1405,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Gurgaon Full-time</t>
+          <t>Bengaluru/ Gurgaon Full-time</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1403,7 +1415,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-689879-implementation-engineer-</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1425,12 +1437,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer (PHP + React.JS)</t>
+          <t>Software Engineer - 3 (Voice)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1440,7 +1452,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1450,7 +1462,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1472,12 +1484,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Product Support Intern (API Integration)</t>
+          <t>Software Engineer 3 (Full Stack)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1497,7 +1509,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-api-integration</t>
+          <t>https://exotel.com/about-us/careers/#op-697293-software-engineer-3-full-stack</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1519,7 +1531,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1534,7 +1546,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru/ Gurgaon Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1544,7 +1556,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1566,7 +1578,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1581,7 +1593,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1591,7 +1603,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1613,12 +1625,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 (Full Stack)</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1638,7 +1650,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-697293-software-engineer-3-full-stack</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1660,7 +1672,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1675,7 +1687,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru Full-time</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1685,7 +1697,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1707,12 +1719,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1722,7 +1734,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1732,7 +1744,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1754,7 +1766,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1779,7 +1791,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1801,7 +1813,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
+          <t>Software Engineer - 3 (Gen AI &amp; Speech)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1816,7 +1828,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru Full-time</t>
+          <t>Bangalore Full-time</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1826,7 +1838,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
+          <t>https://exotel.com/about-us/careers/#op-694350-software-engineer-3-gen-ai--speech</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1848,7 +1860,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Golang/Java/Python)</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1873,7 +1885,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1890,17 +1902,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Ai Engg Intern</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1910,7 +1922,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1920,12 +1932,12 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -1937,17 +1949,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Gen AI &amp; Speech)</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1957,7 +1969,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Bangalore Full-time</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1967,12 +1979,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-694350-software-engineer-3-gen-ai--speech</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1984,17 +1996,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>GenAI Product Builder Intern</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2004,7 +2016,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2014,12 +2026,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2031,17 +2043,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2049,11 +2061,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -2061,12 +2069,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/AI-Engineer_SR-45356-1</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2078,17 +2086,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>SharePoint Full Stack role</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2096,11 +2104,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -2108,12 +2112,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/SharePoint-Full-Stack-role_SR-42495-1</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2125,17 +2129,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>UI Developer - Digital Products</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2143,11 +2147,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/UI-Developer---Digital-Products_SR-45168-1</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>AI Engineer (Platform)</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729957005</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Builder</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -3444,17 +3444,17 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Payroll Industrial Trainee</t>
+          <t>Full Stack Builder</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Payroll Industrial Trainee</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -3538,17 +3538,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Product Operations &amp; Analytics Intern</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/6a5df2a7-5335-41b7-9b50-7f2f5de26d18</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3585,17 +3585,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Sarvam AI</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Product Operations &amp; Analytics Intern</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://jobs.ashbyhq.com/sarvam/6a5df2a7-5335-41b7-9b50-7f2f5de26d18</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://jobs.ashbyhq.com/sarvam</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3632,17 +3632,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3650,7 +3650,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -3658,12 +3662,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3675,17 +3679,17 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Setu</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Video Editor- AI</t>
+          <t>Data Engineer Engineering Â· Data Apply</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3701,12 +3705,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://pinelabsgroup.turbohire.co/get/aDFnNUx</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://setu.co/careers</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3718,17 +3722,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3736,11 +3740,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -3748,12 +3748,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3765,17 +3765,17 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Video Editor- AI</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3783,11 +3783,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -3795,12 +3791,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3812,17 +3808,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Snowflake India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Account Engineer</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3832,7 +3828,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>CO-Colombia-Remote</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3842,12 +3838,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3859,17 +3855,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3877,7 +3873,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -3885,12 +3885,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3902,17 +3902,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Snowflake India</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Account Engineer</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>CO-Colombia-Remote</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://jobs.ashbyhq.com/snowflake</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3949,17 +3949,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3967,11 +3967,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2026-09-03</t>
@@ -3979,12 +3975,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3996,52 +3992,146 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
+          <t>Stripe India</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/stripe</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
           <t>Unacademy</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>Software Engineer, Backend</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>Bengaluru, in</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I78"/>
+  <autoFilter ref="A1:I80"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4120,6 +4210,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4131,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4219,15 +4311,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Vymo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://getvymo.com/careers/</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://getvymo.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4236,18 +4348,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4256,18 +4368,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4276,18 +4388,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4296,18 +4408,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>FirstCry</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.firstcry.com/careers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4316,18 +4428,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4336,18 +4448,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4356,18 +4468,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4376,18 +4488,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
